--- a/data/lossofsale_sg_vatakara.xlsx
+++ b/data/lossofsale_sg_vatakara.xlsx
@@ -1232,6 +1232,271 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="65">
+        <v>19</v>
+      </c>
+      <c t="inlineStr" r="B21">
+        <is>
+          <t xml:space="preserve">26-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C21">
+        <is>
+          <t xml:space="preserve">ARJUN</t>
+        </is>
+      </c>
+      <c r="D21" s="65">
+        <v>9645087061</v>
+      </c>
+      <c t="inlineStr" r="E21">
+        <is>
+          <t xml:space="preserve">01-02-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F21">
+        <is>
+          <t xml:space="preserve">ARJUN P</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G21">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H21">
+        <is>
+          <t xml:space="preserve">SIZE NOT SUITABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I21">
+        <is>
+          <t xml:space="preserve">SIZE TOO LARGE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J21">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K21">
+        <is>
+          <t xml:space="preserve">will come later</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="65">
+        <v>20</v>
+      </c>
+      <c t="inlineStr" r="B22">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C22">
+        <is>
+          <t xml:space="preserve">Akash</t>
+        </is>
+      </c>
+      <c r="D22" s="65">
+        <v>9645945114</v>
+      </c>
+      <c t="inlineStr" r="E22">
+        <is>
+          <t xml:space="preserve">24-02-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F22">
+        <is>
+          <t xml:space="preserve">VISHNU N</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G22">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H22">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I22">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J22">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K22">
+        <is>
+          <t xml:space="preserve">come later</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="65">
+        <v>21</v>
+      </c>
+      <c t="inlineStr" r="B23">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C23">
+        <is>
+          <t xml:space="preserve">Farhan</t>
+        </is>
+      </c>
+      <c r="D23" s="65">
+        <v>9747448657</v>
+      </c>
+      <c t="inlineStr" r="E23">
+        <is>
+          <t xml:space="preserve">04-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F23">
+        <is>
+          <t xml:space="preserve">VISHNU N</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G23">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H23">
+        <is>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I23">
+        <is>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J23">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K23">
+        <is>
+          <t xml:space="preserve">discuss with family</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="65">
+        <v>22</v>
+      </c>
+      <c t="inlineStr" r="B24">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C24">
+        <is>
+          <t xml:space="preserve">Aswanth</t>
+        </is>
+      </c>
+      <c r="D24" s="65">
+        <v>6282331929</v>
+      </c>
+      <c t="inlineStr" r="E24">
+        <is>
+          <t xml:space="preserve">25-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F24">
+        <is>
+          <t xml:space="preserve">VISHNU N</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G24">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H24">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I24">
+        <is>
+          <t xml:space="preserve">Product Already Booked</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J24">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K24">
+        <is>
+          <t xml:space="preserve">liked product is booked for the date</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="65">
+        <v>23</v>
+      </c>
+      <c t="inlineStr" r="B25">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C25">
+        <is>
+          <t xml:space="preserve">Ihsan</t>
+        </is>
+      </c>
+      <c r="D25" s="65">
+        <v>7907877493</v>
+      </c>
+      <c t="inlineStr" r="E25">
+        <is>
+          <t xml:space="preserve">11-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F25">
+        <is>
+          <t xml:space="preserve">VISHNU N</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G25">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H25">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I25">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J25">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K25">
+        <is>
+          <t xml:space="preserve">discuss with family</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
